--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -482,6 +482,8 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -512,7 +514,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>עוברים מהקודם</t>
+          <t>מגיעים מהקודם</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -527,7 +529,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>עוברים מההגשה</t>
+          <t>מגיעים מההגשה</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -538,6 +540,16 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">נמדד על </t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>מהמגויסים עברו כאן</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">נמדד על  </t>
         </is>
       </c>
     </row>
@@ -571,6 +583,14 @@
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="5" t="n"/>
       <c r="K2" s="3" t="n"/>
+      <c r="L2" s="4" t="n">
+        <v>0.514731</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>297 מתוך 577 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -614,6 +634,14 @@
       <c r="K3" s="3" t="n">
         <v>20231</v>
       </c>
+      <c r="L3" s="4" t="n">
+        <v>0.890428</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>707 מתוך 794 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -657,6 +685,14 @@
       <c r="K4" s="3" t="n">
         <v>4002</v>
       </c>
+      <c r="L4" s="4" t="n">
+        <v>0.55603</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>521 מתוך 937 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -700,6 +736,14 @@
       <c r="K5" s="3" t="n">
         <v>2072</v>
       </c>
+      <c r="L5" s="4" t="n">
+        <v>0.530612</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>546 מתוך 1,029 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -743,6 +787,14 @@
       <c r="K6" s="3" t="n">
         <v>1533</v>
       </c>
+      <c r="L6" s="4" t="n">
+        <v>0.720387</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>894 מתוך 1,241 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -786,6 +838,14 @@
       <c r="K7" s="3" t="n">
         <v>424</v>
       </c>
+      <c r="L7" s="4" t="n">
+        <v>0.279819</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>434 מתוך 1,551 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -829,6 +889,14 @@
       <c r="K8" s="3" t="n">
         <v>624</v>
       </c>
+      <c r="L8" s="4" t="n">
+        <v>0.9199079999999999</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1,608 מתוך 1,748 מגויסים</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -871,6 +939,14 @@
       </c>
       <c r="K9" s="7" t="n">
         <v>391</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>2,328 מתוך 2,328 מגויסים</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -881,6 +957,8 @@
 «עוברים מהקודם» ו«עוברים מההגשה» הם שתי מדידות נפרדות, ושתיהן ישירות: איזה חלק מהמועמדים שהיו בשלב האחד הגיעו בפועל לשלב השני אחר כך. «עוברים מההגשה» אינו מכפלה של «עוברים מהקודם» - שרשור אחוזים היה מייצר מספר שאינו קיים בנתונים.
 כל שיעור נמדד בשני בסיסים - חלון זמן קבוע, וקוהורט שהספיק להבשיל - והערך שכאן הוא הממוצע ביניהם. הסיבה: הנתונים קטועים מימין, ומי שביצע פעילות סמוך לסוף התקופה עדיין לא הספיק להתקדם.
 «חציון ימים» נמדד רק על מי שהגיע בפועל לשלב היעד. מי שנעצר בדרך אינו נספר. «נמדד על» הוא מספר המועמדים שעליהם נמדד הזמן הזה.
+«מהמגויסים עברו כאן» היא העמודה החשובה ביותר, והיא אומרת משהו אחר לגמרי משיעור המעבר: איזה חלק מהמגויסים בכלל נרשמו בשלב הזה. שיעור המעבר אומר מה קורה למי שנמצא בשלב; הכיסוי אומר כמה מהגיוסים בכלל עוברים שם. שלב עם כיסוי נמוך אינו יושב מעל כל המשפך, וכמות שמוזנת בו אינה יכולה להסביר את סך הגיוס של הארגון - השאר מגיעים בדרך שאינה עוברת שם ואינה מתועדת בקבצים. הכיסוי נמדד רק על מגויסים שהחלון שלפניהם מכוסה בקבצים, כדי שתחילת הנתונים לא תיראה כמו כיסוי חסר.
+המדידה היא של *הגעה* לשלב, לא של *מעבר* בו. בקובץ אין תוצאה לבדיקת קבצים (0 מתוך 33,254 שורות), ולכן אי אפשר להפריד בין מי שעבר את הבדיקה למי שנכשל בה. «61% מגיעים לבדיקת קבצים» פירושו שבוצעה להם בדיקה, ולא שהם עברו אותה.
 השלב הראשון הוא «הגשות», ולכן אין לו שלב קודם.</t>
         </is>
       </c>
@@ -897,7 +975,7 @@
     <row r="21"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:K21"/>
+    <mergeCell ref="A11:M21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -936,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:17</t>
+          <t>2026-09-02 15:11</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 15:11</t>
+          <t>2026-09-02 15:30</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30</t>
+          <t>2026-09-02 15:42</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 15:42</t>
+          <t>2026-09-03 15:08</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 15:08</t>
+          <t>2026-09-03 19:24</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 19:24</t>
+          <t>2026-09-03 20:04</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 20:04</t>
+          <t>2026-09-03 20:27</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 20:27</t>
+          <t>2026-09-03 20:50</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 20:50</t>
+          <t>2026-09-03 21:21</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:21</t>
+          <t>2026-09-04 00:22</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 00:22</t>
+          <t>2026-09-04 01:00</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 01:00</t>
+          <t>2026-09-04 10:42</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 10:42</t>
+          <t>2026-09-04 12:09</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:09</t>
+          <t>2026-09-04 13:38</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:38</t>
+          <t>2026-09-04 15:17</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 15:17</t>
+          <t>2026-09-04 18:13</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 18:13</t>
+          <t>2026-09-06 08:41</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 08:41</t>
+          <t>2026-09-06 10:05</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 10:05</t>
+          <t>2026-09-06 10:18</t>
         </is>
       </c>
     </row>

--- a/קבצים/התקבל/משפך מיון מלא.xlsx
+++ b/קבצים/התקבל/משפך מיון מלא.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 10:18</t>
+          <t>2026-09-06 11:01</t>
         </is>
       </c>
     </row>
